--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBA95DD-535D-4846-AFEB-B0A8BD37CB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49896437-B54F-4BF8-B299-42FC680209FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="124">
   <si>
     <t>Posicion</t>
   </si>
@@ -408,6 +408,9 @@
   <si>
     <t>K</t>
   </si>
+  <si>
+    <t>Empate</t>
+  </si>
 </sst>
 </file>
 
@@ -778,7 +781,7 @@
         <v>24</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -819,10 +822,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -830,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>39</v>
@@ -841,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>39</v>
@@ -1063,6 +1066,9 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
+      <c r="E2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1206,6 +1212,9 @@
       <c r="J4" t="s">
         <v>35</v>
       </c>
+      <c r="K4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -9672,7 +9681,7 @@
       </c>
       <c r="D508">
         <f t="shared" si="241"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
@@ -16575,7 +16584,7 @@
       </c>
       <c r="D940">
         <f t="shared" si="529"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="941" spans="1:4" x14ac:dyDescent="0.3">

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49896437-B54F-4BF8-B299-42FC680209FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE1AF70-D685-4EA9-83DD-7DBCE817E69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="125">
   <si>
     <t>Posicion</t>
   </si>
@@ -411,6 +411,9 @@
   <si>
     <t>Empate</t>
   </si>
+  <si>
+    <t>Suiza</t>
+  </si>
 </sst>
 </file>
 
@@ -781,7 +784,7 @@
         <v>24</v>
       </c>
       <c r="C2">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -792,7 +795,7 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -803,7 +806,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -814,7 +817,7 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -825,7 +828,7 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -836,7 +839,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -847,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -858,7 +861,7 @@
         <v>13</v>
       </c>
       <c r="C9">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -869,7 +872,7 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -880,7 +883,7 @@
         <v>26</v>
       </c>
       <c r="C11">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -891,7 +894,7 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -899,10 +902,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -910,10 +913,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -921,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -932,10 +935,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -943,7 +946,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>36</v>
@@ -954,10 +957,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C18">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -965,7 +968,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <v>33</v>
@@ -979,7 +982,7 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,7 +993,7 @@
         <v>23</v>
       </c>
       <c r="C21">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,7 +1004,7 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,7 +1015,7 @@
         <v>19</v>
       </c>
       <c r="C23">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1083,6 +1086,9 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1360,13 +1366,16 @@
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="s">
         <v>116</v>
       </c>
       <c r="J11" t="s">
         <v>42</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2887,7 +2896,7 @@
       </c>
       <c r="D83">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -4038,7 +4047,7 @@
       </c>
       <c r="D155">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -5189,7 +5198,7 @@
       </c>
       <c r="D227">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -6340,7 +6349,7 @@
       </c>
       <c r="D299">
         <f t="shared" si="119"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -7491,7 +7500,7 @@
       </c>
       <c r="D371">
         <f t="shared" si="160"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
@@ -9793,7 +9802,7 @@
       </c>
       <c r="D515">
         <f t="shared" ref="D515:D578" si="282">+IF(C515=VLOOKUP(B515,$J$2:$K$73,2,0),3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
@@ -10944,7 +10953,7 @@
       </c>
       <c r="D587">
         <f t="shared" si="324"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -12092,7 +12101,7 @@
       </c>
       <c r="D659">
         <f t="shared" si="366"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
@@ -13243,7 +13252,7 @@
       </c>
       <c r="D731">
         <f t="shared" si="407"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.3">
@@ -14394,7 +14403,7 @@
       </c>
       <c r="D803">
         <f t="shared" si="448"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.3">
@@ -15545,7 +15554,7 @@
       </c>
       <c r="D875">
         <f t="shared" si="488"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="876" spans="1:4" x14ac:dyDescent="0.3">
@@ -16696,7 +16705,7 @@
       </c>
       <c r="D947">
         <f t="shared" si="529"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="948" spans="1:4" x14ac:dyDescent="0.3">
@@ -17847,7 +17856,7 @@
       </c>
       <c r="D1019">
         <f t="shared" si="570"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1020" spans="1:4" x14ac:dyDescent="0.3">
@@ -18998,7 +19007,7 @@
       </c>
       <c r="D1091">
         <f t="shared" ref="D1091:D1154" si="651">+IF(C1091=VLOOKUP(B1091,$J$2:$K$73,2,0),3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1092" spans="1:4" x14ac:dyDescent="0.3">
@@ -20149,7 +20158,7 @@
       </c>
       <c r="D1163">
         <f t="shared" si="693"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
@@ -21300,7 +21309,7 @@
       </c>
       <c r="D1235">
         <f t="shared" si="735"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
@@ -22451,7 +22460,7 @@
       </c>
       <c r="D1307">
         <f t="shared" si="776"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1308" spans="1:4" x14ac:dyDescent="0.3">
@@ -24753,7 +24762,7 @@
       </c>
       <c r="D1451">
         <f t="shared" si="857"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1452" spans="1:4" x14ac:dyDescent="0.3">
@@ -25904,7 +25913,7 @@
       </c>
       <c r="D1523">
         <f t="shared" si="898"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1524" spans="1:4" x14ac:dyDescent="0.3">

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B757923-A91E-4847-AC56-C55F33BA6763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF9E43C-D495-432F-9F78-343CF443F0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -806,7 +806,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -814,10 +814,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -825,10 +825,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -836,10 +836,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -847,10 +847,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -872,7 +872,7 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -880,10 +880,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -891,10 +891,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -902,10 +902,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,10 +913,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C12">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -924,10 +924,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -935,10 +935,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -946,10 +946,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -960,7 +960,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -971,7 +971,7 @@
         <v>31</v>
       </c>
       <c r="C17">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>22</v>
       </c>
       <c r="C18">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,10 +990,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,10 +1001,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1015,7 +1015,7 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1026,7 +1026,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1037,7 +1037,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2525,6 +2525,9 @@
       <c r="K42" t="s">
         <v>82</v>
       </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
       <c r="O42" s="5"/>
       <c r="P42" s="3"/>
       <c r="R42" s="4"/>
@@ -2555,6 +2558,9 @@
       <c r="K43" t="s">
         <v>83</v>
       </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
       <c r="O43" s="5"/>
       <c r="P43" s="3"/>
       <c r="R43" s="4"/>
@@ -2585,6 +2591,9 @@
       <c r="K44" t="s">
         <v>88</v>
       </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
       <c r="O44" s="5"/>
       <c r="P44" s="3"/>
       <c r="R44" s="4"/>
@@ -2615,6 +2624,9 @@
       <c r="K45" t="s">
         <v>89</v>
       </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
       <c r="O45" s="5"/>
       <c r="P45" s="3"/>
       <c r="R45" s="4"/>
@@ -18014,7 +18026,7 @@
       </c>
       <c r="D882">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E882" s="2">
         <v>46195</v>
@@ -18032,7 +18044,7 @@
       </c>
       <c r="D883">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E883" s="2">
         <v>46195</v>
@@ -18050,7 +18062,7 @@
       </c>
       <c r="D884">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E884" s="2">
         <v>46195</v>
@@ -18068,7 +18080,7 @@
       </c>
       <c r="D885">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E885" s="2">
         <v>46195</v>
@@ -18086,7 +18098,7 @@
       </c>
       <c r="D886">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E886" s="2">
         <v>46195</v>
@@ -18122,7 +18134,7 @@
       </c>
       <c r="D888">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E888" s="2">
         <v>46195</v>
@@ -18158,7 +18170,7 @@
       </c>
       <c r="D890">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E890" s="2">
         <v>46195</v>
@@ -18176,7 +18188,7 @@
       </c>
       <c r="D891">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E891" s="2">
         <v>46195</v>
@@ -18212,7 +18224,7 @@
       </c>
       <c r="D893">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E893" s="2">
         <v>46195</v>
@@ -18230,7 +18242,7 @@
       </c>
       <c r="D894">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E894" s="2">
         <v>46195</v>
@@ -18266,7 +18278,7 @@
       </c>
       <c r="D896">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E896" s="2">
         <v>46195</v>
@@ -18284,7 +18296,7 @@
       </c>
       <c r="D897">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E897" s="2">
         <v>46195</v>
@@ -18302,7 +18314,7 @@
       </c>
       <c r="D898">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E898" s="2">
         <v>46195</v>
@@ -18338,7 +18350,7 @@
       </c>
       <c r="D900">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E900" s="2">
         <v>46195</v>
@@ -18356,7 +18368,7 @@
       </c>
       <c r="D901">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E901" s="2">
         <v>46195</v>
@@ -18374,7 +18386,7 @@
       </c>
       <c r="D902">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E902" s="2">
         <v>46195</v>
@@ -18392,7 +18404,7 @@
       </c>
       <c r="D903">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E903" s="2">
         <v>46195</v>
@@ -18410,7 +18422,7 @@
       </c>
       <c r="D904">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E904" s="2">
         <v>46195</v>
@@ -18428,7 +18440,7 @@
       </c>
       <c r="D905">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E905" s="2">
         <v>46195</v>
@@ -18446,7 +18458,7 @@
       </c>
       <c r="D906">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E906" s="2">
         <v>46195</v>
@@ -18482,7 +18494,7 @@
       </c>
       <c r="D908">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E908" s="2">
         <v>46195</v>
@@ -18518,7 +18530,7 @@
       </c>
       <c r="D910">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E910" s="2">
         <v>46195</v>
@@ -18554,7 +18566,7 @@
       </c>
       <c r="D912">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E912" s="2">
         <v>46195</v>
@@ -18572,7 +18584,7 @@
       </c>
       <c r="D913">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E913" s="2">
         <v>46195</v>
@@ -18590,7 +18602,7 @@
       </c>
       <c r="D914">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E914" s="2">
         <v>46195</v>
@@ -18608,7 +18620,7 @@
       </c>
       <c r="D915">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E915" s="2">
         <v>46195</v>
@@ -18626,7 +18638,7 @@
       </c>
       <c r="D916">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E916" s="2">
         <v>46195</v>
@@ -18644,7 +18656,7 @@
       </c>
       <c r="D917">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E917" s="2">
         <v>46195</v>
@@ -18662,7 +18674,7 @@
       </c>
       <c r="D918">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E918" s="2">
         <v>46195</v>
@@ -18680,7 +18692,7 @@
       </c>
       <c r="D919">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E919" s="2">
         <v>46195</v>
@@ -18698,7 +18710,7 @@
       </c>
       <c r="D920">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E920" s="2">
         <v>46195</v>
@@ -18716,7 +18728,7 @@
       </c>
       <c r="D921">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E921" s="2">
         <v>46195</v>
@@ -18734,7 +18746,7 @@
       </c>
       <c r="D922">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E922" s="2">
         <v>46195</v>
@@ -18770,7 +18782,7 @@
       </c>
       <c r="D924">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E924" s="2">
         <v>46195</v>
@@ -18788,7 +18800,7 @@
       </c>
       <c r="D925">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E925" s="2">
         <v>46195</v>
@@ -18806,7 +18818,7 @@
       </c>
       <c r="D926">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E926" s="2">
         <v>46195</v>
@@ -18842,7 +18854,7 @@
       </c>
       <c r="D928">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E928" s="2">
         <v>46195</v>
@@ -18860,7 +18872,7 @@
       </c>
       <c r="D929">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E929" s="2">
         <v>46195</v>
@@ -18878,7 +18890,7 @@
       </c>
       <c r="D930">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E930" s="2">
         <v>46195</v>
@@ -18914,7 +18926,7 @@
       </c>
       <c r="D932">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E932" s="2">
         <v>46195</v>
@@ -18932,7 +18944,7 @@
       </c>
       <c r="D933">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E933" s="2">
         <v>46195</v>
@@ -18950,7 +18962,7 @@
       </c>
       <c r="D934">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E934" s="2">
         <v>46195</v>
@@ -18968,7 +18980,7 @@
       </c>
       <c r="D935">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E935" s="2">
         <v>46195</v>
@@ -18986,7 +18998,7 @@
       </c>
       <c r="D936">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E936" s="2">
         <v>46195</v>
@@ -19004,7 +19016,7 @@
       </c>
       <c r="D937">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E937" s="2">
         <v>46195</v>
@@ -19022,7 +19034,7 @@
       </c>
       <c r="D938">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E938" s="2">
         <v>46195</v>
@@ -19058,7 +19070,7 @@
       </c>
       <c r="D940">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E940" s="2">
         <v>46195</v>
@@ -19076,7 +19088,7 @@
       </c>
       <c r="D941">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E941" s="2">
         <v>46195</v>
@@ -19094,7 +19106,7 @@
       </c>
       <c r="D942">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E942" s="2">
         <v>46195</v>
@@ -19130,7 +19142,7 @@
       </c>
       <c r="D944">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E944" s="2">
         <v>46195</v>
@@ -19148,7 +19160,7 @@
       </c>
       <c r="D945">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E945" s="2">
         <v>46195</v>
@@ -19166,7 +19178,7 @@
       </c>
       <c r="D946">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E946" s="2">
         <v>46195</v>
@@ -19202,7 +19214,7 @@
       </c>
       <c r="D948">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E948" s="2">
         <v>46195</v>
@@ -19220,7 +19232,7 @@
       </c>
       <c r="D949">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E949" s="2">
         <v>46195</v>
@@ -19238,7 +19250,7 @@
       </c>
       <c r="D950">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E950" s="2">
         <v>46195</v>
@@ -19274,7 +19286,7 @@
       </c>
       <c r="D952">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E952" s="2">
         <v>46195</v>
@@ -19292,7 +19304,7 @@
       </c>
       <c r="D953">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E953" s="2">
         <v>46195</v>
@@ -19310,7 +19322,7 @@
       </c>
       <c r="D954">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E954" s="2">
         <v>46195</v>
@@ -19346,7 +19358,7 @@
       </c>
       <c r="D956">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E956" s="2">
         <v>46195</v>
@@ -19364,7 +19376,7 @@
       </c>
       <c r="D957">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E957" s="2">
         <v>46195</v>
@@ -19382,7 +19394,7 @@
       </c>
       <c r="D958">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E958" s="2">
         <v>46195</v>
@@ -19418,7 +19430,7 @@
       </c>
       <c r="D960">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E960" s="2">
         <v>46195</v>
@@ -19454,7 +19466,7 @@
       </c>
       <c r="D962">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E962" s="2">
         <v>46195</v>
@@ -19490,7 +19502,7 @@
       </c>
       <c r="D964">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E964" s="2">
         <v>46195</v>
@@ -19508,7 +19520,7 @@
       </c>
       <c r="D965">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E965" s="2">
         <v>46195</v>
@@ -19526,7 +19538,7 @@
       </c>
       <c r="D966">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E966" s="2">
         <v>46195</v>
@@ -19562,7 +19574,7 @@
       </c>
       <c r="D968">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E968" s="2">
         <v>46195</v>

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF9E43C-D495-432F-9F78-343CF443F0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE94A5D8-5B16-4F01-8EB6-44E706006AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="122">
   <si>
     <t>Posicion</t>
   </si>
@@ -806,7 +806,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -828,7 +828,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -850,7 +850,7 @@
         <v>30</v>
       </c>
       <c r="C6">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -872,7 +872,7 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -883,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -905,7 +905,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -916,7 +916,7 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -927,7 +927,7 @@
         <v>17</v>
       </c>
       <c r="C13">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -938,7 +938,7 @@
         <v>12</v>
       </c>
       <c r="C14">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -949,7 +949,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -957,10 +957,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C16">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -968,10 +968,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>22</v>
       </c>
       <c r="C18">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -993,7 +993,7 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,10 +1001,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,10 +1012,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1026,7 +1026,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1037,7 +1037,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1080,13 +1080,11 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
-        <v>46195</v>
-      </c>
-      <c r="B2" s="8">
-        <v>0.5</v>
-      </c>
+        <v>46196</v>
+      </c>
+      <c r="B2" s="8"/>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1094,13 +1092,11 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>46195</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.66666666666666663</v>
-      </c>
+        <v>46196</v>
+      </c>
+      <c r="B3" s="8"/>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1108,13 +1104,11 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>46195</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.79166666666666663</v>
-      </c>
+        <v>46196</v>
+      </c>
+      <c r="B4" s="8"/>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1122,19 +1116,37 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>46195</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.91666666666666663</v>
-      </c>
+        <v>46196</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -2657,6 +2669,9 @@
       <c r="K46" t="s">
         <v>94</v>
       </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
       <c r="O46" s="5"/>
       <c r="P46" s="3"/>
       <c r="R46" s="4"/>
@@ -2687,6 +2702,9 @@
       <c r="K47" t="s">
         <v>95</v>
       </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
       <c r="O47" s="5"/>
       <c r="P47" s="3"/>
       <c r="R47" s="4"/>
@@ -2717,6 +2735,9 @@
       <c r="K48" t="s">
         <v>100</v>
       </c>
+      <c r="L48" t="s">
+        <v>104</v>
+      </c>
       <c r="O48" s="5"/>
       <c r="P48" s="3"/>
       <c r="R48" s="4"/>
@@ -2747,6 +2768,9 @@
       <c r="K49" t="s">
         <v>101</v>
       </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
       <c r="O49" s="5"/>
       <c r="P49" s="3"/>
       <c r="R49" s="4"/>
@@ -19610,7 +19634,7 @@
       </c>
       <c r="D970">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E970" s="2">
         <v>46196</v>
@@ -19628,7 +19652,7 @@
       </c>
       <c r="D971">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E971" s="2">
         <v>46196</v>
@@ -19682,7 +19706,7 @@
       </c>
       <c r="D974">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E974" s="2">
         <v>46196</v>
@@ -19700,7 +19724,7 @@
       </c>
       <c r="D975">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E975" s="2">
         <v>46196</v>
@@ -19718,7 +19742,7 @@
       </c>
       <c r="D976">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E976" s="2">
         <v>46196</v>
@@ -19736,7 +19760,7 @@
       </c>
       <c r="D977">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E977" s="2">
         <v>46196</v>
@@ -19754,7 +19778,7 @@
       </c>
       <c r="D978">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E978" s="2">
         <v>46196</v>
@@ -19772,7 +19796,7 @@
       </c>
       <c r="D979">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E979" s="2">
         <v>46196</v>
@@ -19808,7 +19832,7 @@
       </c>
       <c r="D981">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E981" s="2">
         <v>46196</v>
@@ -19826,7 +19850,7 @@
       </c>
       <c r="D982">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E982" s="2">
         <v>46196</v>
@@ -19844,7 +19868,7 @@
       </c>
       <c r="D983">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E983" s="2">
         <v>46196</v>
@@ -19880,7 +19904,7 @@
       </c>
       <c r="D985">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E985" s="2">
         <v>46196</v>
@@ -19898,7 +19922,7 @@
       </c>
       <c r="D986">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E986" s="2">
         <v>46196</v>
@@ -19916,7 +19940,7 @@
       </c>
       <c r="D987">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E987" s="2">
         <v>46196</v>
@@ -19952,7 +19976,7 @@
       </c>
       <c r="D989">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E989" s="2">
         <v>46196</v>
@@ -19970,7 +19994,7 @@
       </c>
       <c r="D990">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E990" s="2">
         <v>46196</v>
@@ -19988,7 +20012,7 @@
       </c>
       <c r="D991">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E991" s="2">
         <v>46196</v>
@@ -20024,7 +20048,7 @@
       </c>
       <c r="D993">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E993" s="2">
         <v>46196</v>
@@ -20042,7 +20066,7 @@
       </c>
       <c r="D994">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E994" s="2">
         <v>46196</v>
@@ -20060,7 +20084,7 @@
       </c>
       <c r="D995">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E995" s="2">
         <v>46196</v>
@@ -20114,7 +20138,7 @@
       </c>
       <c r="D998">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E998" s="2">
         <v>46196</v>
@@ -20132,7 +20156,7 @@
       </c>
       <c r="D999">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E999" s="2">
         <v>46196</v>
@@ -20168,7 +20192,7 @@
       </c>
       <c r="D1001">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1001" s="2">
         <v>46196</v>
@@ -20186,7 +20210,7 @@
       </c>
       <c r="D1002">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1002" s="2">
         <v>46196</v>
@@ -20204,7 +20228,7 @@
       </c>
       <c r="D1003">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1003" s="2">
         <v>46196</v>
@@ -20240,7 +20264,7 @@
       </c>
       <c r="D1005">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1005" s="2">
         <v>46196</v>
@@ -20258,7 +20282,7 @@
       </c>
       <c r="D1006">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1006" s="2">
         <v>46196</v>
@@ -20276,7 +20300,7 @@
       </c>
       <c r="D1007">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1007" s="2">
         <v>46196</v>
@@ -20312,7 +20336,7 @@
       </c>
       <c r="D1009">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1009" s="2">
         <v>46196</v>
@@ -20330,7 +20354,7 @@
       </c>
       <c r="D1010">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1010" s="2">
         <v>46196</v>
@@ -20348,7 +20372,7 @@
       </c>
       <c r="D1011">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1011" s="2">
         <v>46196</v>
@@ -20384,7 +20408,7 @@
       </c>
       <c r="D1013">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1013" s="2">
         <v>46196</v>
@@ -20402,7 +20426,7 @@
       </c>
       <c r="D1014">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1014" s="2">
         <v>46196</v>
@@ -20420,7 +20444,7 @@
       </c>
       <c r="D1015">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1015" s="2">
         <v>46196</v>
@@ -20456,7 +20480,7 @@
       </c>
       <c r="D1017">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1017" s="2">
         <v>46196</v>
@@ -20474,7 +20498,7 @@
       </c>
       <c r="D1018">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1018" s="2">
         <v>46196</v>
@@ -20492,7 +20516,7 @@
       </c>
       <c r="D1019">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1019" s="2">
         <v>46196</v>
@@ -20528,7 +20552,7 @@
       </c>
       <c r="D1021">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1021" s="2">
         <v>46196</v>
@@ -20546,7 +20570,7 @@
       </c>
       <c r="D1022">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1022" s="2">
         <v>46196</v>
@@ -20564,7 +20588,7 @@
       </c>
       <c r="D1023">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1023" s="2">
         <v>46196</v>
@@ -20600,7 +20624,7 @@
       </c>
       <c r="D1025">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1025" s="2">
         <v>46196</v>
@@ -20618,7 +20642,7 @@
       </c>
       <c r="D1026">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1026" s="2">
         <v>46196</v>
@@ -20636,7 +20660,7 @@
       </c>
       <c r="D1027">
         <f t="shared" ref="D1027:D1090" si="16">+IF(VLOOKUP(B1027,$K$2:$L$73,2,0)=C1027,3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1027" s="2">
         <v>46196</v>
@@ -20672,7 +20696,7 @@
       </c>
       <c r="D1029">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1029" s="2">
         <v>46196</v>
@@ -20690,7 +20714,7 @@
       </c>
       <c r="D1030">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1030" s="2">
         <v>46196</v>
@@ -20708,7 +20732,7 @@
       </c>
       <c r="D1031">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1031" s="2">
         <v>46196</v>
@@ -20744,7 +20768,7 @@
       </c>
       <c r="D1033">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1033" s="2">
         <v>46196</v>
@@ -20762,7 +20786,7 @@
       </c>
       <c r="D1034">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1034" s="2">
         <v>46196</v>
@@ -20780,7 +20804,7 @@
       </c>
       <c r="D1035">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1035" s="2">
         <v>46196</v>
@@ -20798,7 +20822,7 @@
       </c>
       <c r="D1036">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1036" s="2">
         <v>46196</v>
@@ -20816,7 +20840,7 @@
       </c>
       <c r="D1037">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1037" s="2">
         <v>46196</v>
@@ -20834,7 +20858,7 @@
       </c>
       <c r="D1038">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1038" s="2">
         <v>46196</v>
@@ -20852,7 +20876,7 @@
       </c>
       <c r="D1039">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1039" s="2">
         <v>46196</v>
@@ -20888,7 +20912,7 @@
       </c>
       <c r="D1041">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1041" s="2">
         <v>46196</v>
@@ -20906,7 +20930,7 @@
       </c>
       <c r="D1042">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1042" s="2">
         <v>46196</v>
@@ -20924,7 +20948,7 @@
       </c>
       <c r="D1043">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1043" s="2">
         <v>46196</v>
@@ -20960,7 +20984,7 @@
       </c>
       <c r="D1045">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1045" s="2">
         <v>46196</v>
@@ -20978,7 +21002,7 @@
       </c>
       <c r="D1046">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1046" s="2">
         <v>46196</v>
@@ -21014,7 +21038,7 @@
       </c>
       <c r="D1048">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1048" s="2">
         <v>46196</v>
@@ -21032,7 +21056,7 @@
       </c>
       <c r="D1049">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1049" s="2">
         <v>46196</v>
@@ -21050,7 +21074,7 @@
       </c>
       <c r="D1050">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1050" s="2">
         <v>46196</v>
@@ -21068,7 +21092,7 @@
       </c>
       <c r="D1051">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1051" s="2">
         <v>46196</v>
@@ -21104,7 +21128,7 @@
       </c>
       <c r="D1053">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1053" s="2">
         <v>46196</v>
@@ -21122,7 +21146,7 @@
       </c>
       <c r="D1054">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1054" s="2">
         <v>46196</v>
@@ -21140,7 +21164,7 @@
       </c>
       <c r="D1055">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1055" s="2">
         <v>46196</v>
@@ -21176,7 +21200,7 @@
       </c>
       <c r="D1057">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1057" s="2">
         <v>46196</v>

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE94A5D8-5B16-4F01-8EB6-44E706006AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3686A5-E8FA-41C7-B354-0BC7ECD2C231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -785,6 +785,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -806,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -817,7 +818,7 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -828,7 +829,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -836,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -847,10 +848,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -858,10 +859,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -869,10 +870,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -883,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -894,7 +895,7 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -905,7 +906,7 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,10 +914,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -924,10 +925,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -935,10 +936,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C14">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -946,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -957,10 +958,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -968,10 +969,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -979,10 +980,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,10 +991,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,10 +1002,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1015,7 +1016,7 @@
         <v>16</v>
       </c>
       <c r="C21">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1026,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1037,7 +1038,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2801,6 +2802,9 @@
       <c r="K50" t="s">
         <v>36</v>
       </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
       <c r="O50" s="5"/>
       <c r="P50" s="3"/>
       <c r="R50" s="4"/>
@@ -2831,6 +2835,9 @@
       <c r="K51" t="s">
         <v>37</v>
       </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
       <c r="O51" s="5"/>
       <c r="P51" s="3"/>
       <c r="R51" s="4"/>
@@ -2861,6 +2868,9 @@
       <c r="K52" t="s">
         <v>42</v>
       </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
       <c r="O52" s="5"/>
       <c r="P52" s="3"/>
       <c r="R52" s="4"/>
@@ -2891,6 +2901,9 @@
       <c r="K53" t="s">
         <v>43</v>
       </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
       <c r="O53" s="5"/>
       <c r="P53" s="3"/>
       <c r="R53" s="4"/>
@@ -2921,6 +2934,9 @@
       <c r="K54" t="s">
         <v>48</v>
       </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
       <c r="O54" s="5"/>
       <c r="P54" s="3"/>
       <c r="R54" s="4"/>
@@ -2951,6 +2967,9 @@
       <c r="K55" t="s">
         <v>49</v>
       </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
       <c r="O55" s="5"/>
       <c r="P55" s="3"/>
       <c r="R55" s="4"/>
@@ -21272,7 +21291,7 @@
       </c>
       <c r="D1061">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1061" s="2">
         <v>46197</v>
@@ -21290,7 +21309,7 @@
       </c>
       <c r="D1062">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1062" s="2">
         <v>46197</v>
@@ -21308,7 +21327,7 @@
       </c>
       <c r="D1063">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1063" s="2">
         <v>46197</v>
@@ -21380,7 +21399,7 @@
       </c>
       <c r="D1067">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1067" s="2">
         <v>46197</v>
@@ -21398,7 +21417,7 @@
       </c>
       <c r="D1068">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1068" s="2">
         <v>46197</v>
@@ -21416,7 +21435,7 @@
       </c>
       <c r="D1069">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1069" s="2">
         <v>46197</v>
@@ -21434,7 +21453,7 @@
       </c>
       <c r="D1070">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1070" s="2">
         <v>46197</v>
@@ -21470,7 +21489,7 @@
       </c>
       <c r="D1072">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1072" s="2">
         <v>46197</v>
@@ -21506,7 +21525,7 @@
       </c>
       <c r="D1074">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1074" s="2">
         <v>46197</v>
@@ -21524,7 +21543,7 @@
       </c>
       <c r="D1075">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1075" s="2">
         <v>46197</v>
@@ -21596,7 +21615,7 @@
       </c>
       <c r="D1079">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1079" s="2">
         <v>46197</v>
@@ -21686,7 +21705,7 @@
       </c>
       <c r="D1084">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1084" s="2">
         <v>46197</v>
@@ -21704,7 +21723,7 @@
       </c>
       <c r="D1085">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1085" s="2">
         <v>46197</v>
@@ -21722,7 +21741,7 @@
       </c>
       <c r="D1086">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1086" s="2">
         <v>46197</v>
@@ -21740,7 +21759,7 @@
       </c>
       <c r="D1087">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1087" s="2">
         <v>46197</v>
@@ -21776,7 +21795,7 @@
       </c>
       <c r="D1089">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1089" s="2">
         <v>46197</v>
@@ -21830,7 +21849,7 @@
       </c>
       <c r="D1092">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1092" s="2">
         <v>46197</v>
@@ -21848,7 +21867,7 @@
       </c>
       <c r="D1093">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1093" s="2">
         <v>46197</v>
@@ -21884,7 +21903,7 @@
       </c>
       <c r="D1095">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1095" s="2">
         <v>46197</v>
@@ -21920,7 +21939,7 @@
       </c>
       <c r="D1097">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1097" s="2">
         <v>46197</v>
@@ -21938,7 +21957,7 @@
       </c>
       <c r="D1098">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1098" s="2">
         <v>46197</v>
@@ -21956,7 +21975,7 @@
       </c>
       <c r="D1099">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1099" s="2">
         <v>46197</v>
@@ -21992,7 +22011,7 @@
       </c>
       <c r="D1101">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1101" s="2">
         <v>46197</v>
@@ -22028,7 +22047,7 @@
       </c>
       <c r="D1103">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1103" s="2">
         <v>46197</v>
@@ -22046,7 +22065,7 @@
       </c>
       <c r="D1104">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1104" s="2">
         <v>46197</v>
@@ -22064,7 +22083,7 @@
       </c>
       <c r="D1105">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1105" s="2">
         <v>46197</v>
@@ -22136,7 +22155,7 @@
       </c>
       <c r="D1109">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1109" s="2">
         <v>46197</v>
@@ -22154,7 +22173,7 @@
       </c>
       <c r="D1110">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1110" s="2">
         <v>46197</v>
@@ -22172,7 +22191,7 @@
       </c>
       <c r="D1111">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1111" s="2">
         <v>46197</v>
@@ -22208,7 +22227,7 @@
       </c>
       <c r="D1113">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1113" s="2">
         <v>46197</v>
@@ -22244,7 +22263,7 @@
       </c>
       <c r="D1115">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1115" s="2">
         <v>46197</v>
@@ -22262,7 +22281,7 @@
       </c>
       <c r="D1116">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1116" s="2">
         <v>46197</v>
@@ -22280,7 +22299,7 @@
       </c>
       <c r="D1117">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1117" s="2">
         <v>46197</v>
@@ -22316,7 +22335,7 @@
       </c>
       <c r="D1119">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1119" s="2">
         <v>46197</v>
@@ -22370,7 +22389,7 @@
       </c>
       <c r="D1122">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1122" s="2">
         <v>46197</v>
@@ -22388,7 +22407,7 @@
       </c>
       <c r="D1123">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1123" s="2">
         <v>46197</v>
@@ -22424,7 +22443,7 @@
       </c>
       <c r="D1125">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1125" s="2">
         <v>46197</v>
@@ -22478,7 +22497,7 @@
       </c>
       <c r="D1128">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1128" s="2">
         <v>46197</v>
@@ -22496,7 +22515,7 @@
       </c>
       <c r="D1129">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1129" s="2">
         <v>46197</v>
@@ -22532,7 +22551,7 @@
       </c>
       <c r="D1131">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1131" s="2">
         <v>46197</v>
@@ -22550,7 +22569,7 @@
       </c>
       <c r="D1132">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1132" s="2">
         <v>46197</v>
@@ -22568,7 +22587,7 @@
       </c>
       <c r="D1133">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1133" s="2">
         <v>46197</v>
@@ -22586,7 +22605,7 @@
       </c>
       <c r="D1134">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1134" s="2">
         <v>46197</v>
@@ -22604,7 +22623,7 @@
       </c>
       <c r="D1135">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1135" s="2">
         <v>46197</v>
@@ -22640,7 +22659,7 @@
       </c>
       <c r="D1137">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1137" s="2">
         <v>46197</v>
@@ -22658,7 +22677,7 @@
       </c>
       <c r="D1138">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1138" s="2">
         <v>46197</v>
@@ -22694,7 +22713,7 @@
       </c>
       <c r="D1140">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1140" s="2">
         <v>46197</v>
@@ -22712,7 +22731,7 @@
       </c>
       <c r="D1141">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1141" s="2">
         <v>46197</v>
@@ -22766,7 +22785,7 @@
       </c>
       <c r="D1144">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1144" s="2">
         <v>46197</v>
@@ -22784,7 +22803,7 @@
       </c>
       <c r="D1145">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1145" s="2">
         <v>46197</v>
@@ -22802,7 +22821,7 @@
       </c>
       <c r="D1146">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1146" s="2">
         <v>46197</v>
@@ -22820,7 +22839,7 @@
       </c>
       <c r="D1147">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1147" s="2">
         <v>46197</v>
@@ -22892,7 +22911,7 @@
       </c>
       <c r="D1151">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1151" s="2">
         <v>46197</v>
@@ -22910,7 +22929,7 @@
       </c>
       <c r="D1152">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1152" s="2">
         <v>46197</v>
@@ -22928,7 +22947,7 @@
       </c>
       <c r="D1153">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1153" s="2">
         <v>46197</v>
@@ -23000,7 +23019,7 @@
       </c>
       <c r="D1157">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1157" s="2">
         <v>46197</v>
@@ -23018,7 +23037,7 @@
       </c>
       <c r="D1158">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1158" s="2">
         <v>46197</v>
@@ -23036,7 +23055,7 @@
       </c>
       <c r="D1159">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1159" s="2">
         <v>46197</v>
@@ -23054,7 +23073,7 @@
       </c>
       <c r="D1160">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1160" s="2">
         <v>46197</v>
@@ -23072,7 +23091,7 @@
       </c>
       <c r="D1161">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1161" s="2">
         <v>46197</v>
@@ -23090,7 +23109,7 @@
       </c>
       <c r="D1162">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1162" s="2">
         <v>46197</v>
@@ -23126,7 +23145,7 @@
       </c>
       <c r="D1164">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1164" s="2">
         <v>46197</v>
@@ -23144,7 +23163,7 @@
       </c>
       <c r="D1165">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1165" s="2">
         <v>46197</v>
@@ -23180,7 +23199,7 @@
       </c>
       <c r="D1167">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1167" s="2">
         <v>46197</v>
@@ -23234,7 +23253,7 @@
       </c>
       <c r="D1170">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1170" s="2">
         <v>46197</v>
@@ -23252,7 +23271,7 @@
       </c>
       <c r="D1171">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1171" s="2">
         <v>46197</v>
@@ -23306,7 +23325,7 @@
       </c>
       <c r="D1174">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1174" s="2">
         <v>46197</v>
@@ -23342,7 +23361,7 @@
       </c>
       <c r="D1176">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1176" s="2">
         <v>46197</v>
@@ -23360,7 +23379,7 @@
       </c>
       <c r="D1177">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1177" s="2">
         <v>46197</v>
@@ -23414,7 +23433,7 @@
       </c>
       <c r="D1180">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1180" s="2">
         <v>46197</v>
@@ -23432,7 +23451,7 @@
       </c>
       <c r="D1181">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1181" s="2">
         <v>46197</v>
@@ -23450,7 +23469,7 @@
       </c>
       <c r="D1182">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1182" s="2">
         <v>46197</v>
@@ -23468,7 +23487,7 @@
       </c>
       <c r="D1183">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1183" s="2">
         <v>46197</v>
@@ -23486,7 +23505,7 @@
       </c>
       <c r="D1184">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1184" s="2">
         <v>46197</v>
@@ -23522,7 +23541,7 @@
       </c>
       <c r="D1186">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1186" s="2">
         <v>46197</v>
@@ -23540,7 +23559,7 @@
       </c>
       <c r="D1187">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1187" s="2">
         <v>46197</v>
@@ -23558,7 +23577,7 @@
       </c>
       <c r="D1188">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1188" s="2">
         <v>46197</v>
@@ -23576,7 +23595,7 @@
       </c>
       <c r="D1189">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1189" s="2">
         <v>46197</v>

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3686A5-E8FA-41C7-B354-0BC7ECD2C231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C194E92-274A-40FF-87B1-6E9EAB824E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="122">
   <si>
     <t>Posicion</t>
   </si>
@@ -807,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -818,7 +818,7 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -829,7 +829,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -848,10 +848,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -859,10 +859,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -870,10 +870,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -892,10 +892,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -903,10 +903,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C11">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -914,10 +914,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -925,10 +925,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -936,10 +936,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -947,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -961,7 +961,7 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -969,10 +969,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -983,7 +983,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -994,7 +994,7 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1005,7 +1005,7 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1016,7 +1016,7 @@
         <v>16</v>
       </c>
       <c r="C21">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1027,7 +1027,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1038,7 +1038,7 @@
         <v>18</v>
       </c>
       <c r="C23">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3000,6 +3000,9 @@
       <c r="K56" t="s">
         <v>54</v>
       </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
       <c r="O56" s="5"/>
       <c r="P56" s="3"/>
       <c r="R56" s="4"/>
@@ -3030,6 +3033,9 @@
       <c r="K57" t="s">
         <v>55</v>
       </c>
+      <c r="L57" t="s">
+        <v>104</v>
+      </c>
       <c r="O57" s="5"/>
       <c r="P57" s="3"/>
       <c r="R57" s="4"/>
@@ -3060,6 +3066,9 @@
       <c r="K58" t="s">
         <v>60</v>
       </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
       <c r="O58" s="5"/>
       <c r="P58" s="3"/>
       <c r="R58" s="4"/>
@@ -3090,6 +3099,9 @@
       <c r="K59" t="s">
         <v>61</v>
       </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
       <c r="O59" s="5"/>
       <c r="P59" s="3"/>
       <c r="R59" s="4"/>
@@ -3120,6 +3132,9 @@
       <c r="K60" t="s">
         <v>66</v>
       </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
       <c r="O60" s="5"/>
       <c r="P60" s="3"/>
       <c r="R60" s="4"/>
@@ -3150,6 +3165,9 @@
       <c r="K61" t="s">
         <v>67</v>
       </c>
+      <c r="L61" t="s">
+        <v>104</v>
+      </c>
       <c r="O61" s="5"/>
       <c r="P61" s="3"/>
       <c r="R61" s="4"/>
@@ -23649,7 +23667,7 @@
       </c>
       <c r="D1192">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1192" s="2">
         <v>46198</v>
@@ -23685,7 +23703,7 @@
       </c>
       <c r="D1194">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1194" s="2">
         <v>46198</v>
@@ -23757,7 +23775,7 @@
       </c>
       <c r="D1198">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1198" s="2">
         <v>46198</v>
@@ -23793,7 +23811,7 @@
       </c>
       <c r="D1200">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1200" s="2">
         <v>46198</v>
@@ -23829,7 +23847,7 @@
       </c>
       <c r="D1202">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1202" s="2">
         <v>46198</v>
@@ -23865,7 +23883,7 @@
       </c>
       <c r="D1204">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1204" s="2">
         <v>46198</v>
@@ -23901,7 +23919,7 @@
       </c>
       <c r="D1206">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1206" s="2">
         <v>46198</v>
@@ -23919,7 +23937,7 @@
       </c>
       <c r="D1207">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1207" s="2">
         <v>46198</v>
@@ -23955,7 +23973,7 @@
       </c>
       <c r="D1209">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1209" s="2">
         <v>46198</v>
@@ -23973,7 +23991,7 @@
       </c>
       <c r="D1210">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1210" s="2">
         <v>46198</v>
@@ -24009,7 +24027,7 @@
       </c>
       <c r="D1212">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1212" s="2">
         <v>46198</v>
@@ -24027,7 +24045,7 @@
       </c>
       <c r="D1213">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1213" s="2">
         <v>46198</v>
@@ -24081,7 +24099,7 @@
       </c>
       <c r="D1216">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1216" s="2">
         <v>46198</v>
@@ -24117,7 +24135,7 @@
       </c>
       <c r="D1218">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1218" s="2">
         <v>46198</v>
@@ -24153,7 +24171,7 @@
       </c>
       <c r="D1220">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1220" s="2">
         <v>46198</v>
@@ -24189,7 +24207,7 @@
       </c>
       <c r="D1222">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1222" s="2">
         <v>46198</v>
@@ -24225,7 +24243,7 @@
       </c>
       <c r="D1224">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1224" s="2">
         <v>46198</v>
@@ -24297,7 +24315,7 @@
       </c>
       <c r="D1228">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1228" s="2">
         <v>46198</v>
@@ -24333,7 +24351,7 @@
       </c>
       <c r="D1230">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1230" s="2">
         <v>46198</v>
@@ -24351,7 +24369,7 @@
       </c>
       <c r="D1231">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1231" s="2">
         <v>46198</v>
@@ -24405,7 +24423,7 @@
       </c>
       <c r="D1234">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1234" s="2">
         <v>46198</v>
@@ -24441,7 +24459,7 @@
       </c>
       <c r="D1236">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1236" s="2">
         <v>46198</v>
@@ -24459,7 +24477,7 @@
       </c>
       <c r="D1237">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1237" s="2">
         <v>46198</v>
@@ -24477,7 +24495,7 @@
       </c>
       <c r="D1238">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1238" s="2">
         <v>46198</v>
@@ -24513,7 +24531,7 @@
       </c>
       <c r="D1240">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1240" s="2">
         <v>46198</v>
@@ -24549,7 +24567,7 @@
       </c>
       <c r="D1242">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1242" s="2">
         <v>46198</v>
@@ -24567,7 +24585,7 @@
       </c>
       <c r="D1243">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1243" s="2">
         <v>46198</v>
@@ -24621,7 +24639,7 @@
       </c>
       <c r="D1246">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1246" s="2">
         <v>46198</v>
@@ -24657,7 +24675,7 @@
       </c>
       <c r="D1248">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1248" s="2">
         <v>46198</v>
@@ -24729,7 +24747,7 @@
       </c>
       <c r="D1252">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1252" s="2">
         <v>46198</v>
@@ -24765,7 +24783,7 @@
       </c>
       <c r="D1254">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1254" s="2">
         <v>46198</v>
@@ -24801,7 +24819,7 @@
       </c>
       <c r="D1256">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1256" s="2">
         <v>46198</v>
@@ -24837,7 +24855,7 @@
       </c>
       <c r="D1258">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1258" s="2">
         <v>46198</v>
@@ -24873,7 +24891,7 @@
       </c>
       <c r="D1260">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1260" s="2">
         <v>46198</v>
@@ -24909,7 +24927,7 @@
       </c>
       <c r="D1262">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1262" s="2">
         <v>46198</v>
@@ -24945,7 +24963,7 @@
       </c>
       <c r="D1264">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1264" s="2">
         <v>46198</v>
@@ -24981,7 +24999,7 @@
       </c>
       <c r="D1266">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1266" s="2">
         <v>46198</v>
@@ -25053,7 +25071,7 @@
       </c>
       <c r="D1270">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1270" s="2">
         <v>46198</v>
@@ -25089,7 +25107,7 @@
       </c>
       <c r="D1272">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1272" s="2">
         <v>46198</v>
@@ -25107,7 +25125,7 @@
       </c>
       <c r="D1273">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1273" s="2">
         <v>46198</v>
@@ -25161,7 +25179,7 @@
       </c>
       <c r="D1276">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1276" s="2">
         <v>46198</v>
@@ -25197,7 +25215,7 @@
       </c>
       <c r="D1278">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1278" s="2">
         <v>46198</v>
@@ -25215,7 +25233,7 @@
       </c>
       <c r="D1279">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1279" s="2">
         <v>46198</v>
@@ -25269,7 +25287,7 @@
       </c>
       <c r="D1282">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1282" s="2">
         <v>46198</v>
@@ -25305,7 +25323,7 @@
       </c>
       <c r="D1284">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1284" s="2">
         <v>46198</v>
@@ -25341,7 +25359,7 @@
       </c>
       <c r="D1286">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1286" s="2">
         <v>46198</v>
@@ -25377,7 +25395,7 @@
       </c>
       <c r="D1288">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1288" s="2">
         <v>46198</v>
@@ -25413,7 +25431,7 @@
       </c>
       <c r="D1290">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1290" s="2">
         <v>46198</v>
@@ -25431,7 +25449,7 @@
       </c>
       <c r="D1291">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1291" s="2">
         <v>46198</v>
@@ -25503,7 +25521,7 @@
       </c>
       <c r="D1295">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1295" s="2">
         <v>46198</v>
@@ -25521,7 +25539,7 @@
       </c>
       <c r="D1296">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1296" s="2">
         <v>46198</v>
@@ -25593,7 +25611,7 @@
       </c>
       <c r="D1300">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1300" s="2">
         <v>46198</v>
@@ -25629,7 +25647,7 @@
       </c>
       <c r="D1302">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1302" s="2">
         <v>46198</v>
@@ -25683,7 +25701,7 @@
       </c>
       <c r="D1305">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1305" s="2">
         <v>46198</v>
@@ -25701,7 +25719,7 @@
       </c>
       <c r="D1306">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1306" s="2">
         <v>46198</v>
@@ -25737,7 +25755,7 @@
       </c>
       <c r="D1308">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1308" s="2">
         <v>46198</v>
@@ -25755,7 +25773,7 @@
       </c>
       <c r="D1309">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1309" s="2">
         <v>46198</v>
@@ -25809,7 +25827,7 @@
       </c>
       <c r="D1312">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1312" s="2">
         <v>46198</v>
@@ -25845,7 +25863,7 @@
       </c>
       <c r="D1314">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1314" s="2">
         <v>46198</v>
@@ -25917,7 +25935,7 @@
       </c>
       <c r="D1318">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1318" s="2">
         <v>46198</v>
@@ -25953,7 +25971,7 @@
       </c>
       <c r="D1320">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1320" s="2">
         <v>46198</v>

--- a/Polla_Mundial_CFI.xlsx
+++ b/Polla_Mundial_CFI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AGA\Desktop\Comercial\3.Otros\2026\13. pAIGNA WEB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C194E92-274A-40FF-87B1-6E9EAB824E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32DE3CB-7FBD-477A-88FB-A53F86FB2115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3611" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3615" uniqueCount="122">
   <si>
     <t>Posicion</t>
   </si>
@@ -804,10 +804,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>117</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -815,10 +815,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>114</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -826,10 +826,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -837,10 +837,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -848,10 +848,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>108</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -859,10 +859,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -870,10 +870,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -884,7 +884,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -895,7 +895,7 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -903,10 +903,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -914,10 +914,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -925,10 +925,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -936,10 +936,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C14">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -947,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -958,10 +958,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -969,10 +969,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -980,10 +980,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -991,10 +991,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C19">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1002,10 +1002,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1013,10 +1013,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1024,10 +1024,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1035,10 +1035,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>93</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3198,6 +3198,9 @@
       <c r="K62" t="s">
         <v>72</v>
       </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
       <c r="O62" s="5"/>
       <c r="P62" s="3"/>
       <c r="R62" s="4"/>
@@ -3228,6 +3231,9 @@
       <c r="K63" t="s">
         <v>73</v>
       </c>
+      <c r="L63" t="s">
+        <v>104</v>
+      </c>
       <c r="O63" s="5"/>
       <c r="P63" s="3"/>
       <c r="R63" s="4"/>
@@ -3258,6 +3264,9 @@
       <c r="K64" t="s">
         <v>78</v>
       </c>
+      <c r="L64" t="s">
+        <v>104</v>
+      </c>
       <c r="O64" s="5"/>
       <c r="P64" s="3"/>
       <c r="R64" s="4"/>
@@ -3288,6 +3297,9 @@
       <c r="K65" t="s">
         <v>79</v>
       </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
       <c r="O65" s="5"/>
       <c r="P65" s="3"/>
       <c r="R65" s="4"/>
@@ -3318,6 +3330,9 @@
       <c r="K66" t="s">
         <v>84</v>
       </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
       <c r="O66" s="5"/>
       <c r="P66" s="3"/>
       <c r="R66" s="4"/>
@@ -3348,6 +3363,9 @@
       <c r="K67" t="s">
         <v>85</v>
       </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
       <c r="O67" s="5"/>
       <c r="P67" s="3"/>
       <c r="R67" s="4"/>
@@ -3378,6 +3396,9 @@
       <c r="K68" t="s">
         <v>90</v>
       </c>
+      <c r="L68" t="s">
+        <v>104</v>
+      </c>
       <c r="O68" s="5"/>
       <c r="P68" s="3"/>
       <c r="R68" s="4"/>
@@ -3408,6 +3429,9 @@
       <c r="K69" t="s">
         <v>91</v>
       </c>
+      <c r="L69">
+        <v>2</v>
+      </c>
       <c r="O69" s="5"/>
       <c r="P69" s="3"/>
       <c r="R69" s="4"/>
@@ -3438,6 +3462,9 @@
       <c r="K70" t="s">
         <v>96</v>
       </c>
+      <c r="L70" t="s">
+        <v>104</v>
+      </c>
       <c r="O70" s="5"/>
       <c r="P70" s="3"/>
       <c r="R70" s="4"/>
@@ -3468,6 +3495,9 @@
       <c r="K71" t="s">
         <v>97</v>
       </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
       <c r="O71" s="5"/>
       <c r="P71" s="3"/>
       <c r="R71" s="4"/>
@@ -3498,6 +3528,9 @@
       <c r="K72" t="s">
         <v>102</v>
       </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
       <c r="O72" s="5"/>
       <c r="P72" s="3"/>
       <c r="R72" s="4"/>
@@ -3528,6 +3561,9 @@
       <c r="K73" t="s">
         <v>103</v>
       </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
       <c r="O73" s="5"/>
       <c r="P73" s="3"/>
       <c r="R73" s="4"/>
@@ -26007,7 +26043,7 @@
       </c>
       <c r="D1322">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1322" s="2">
         <v>46199</v>
@@ -26061,7 +26097,7 @@
       </c>
       <c r="D1325">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1325" s="2">
         <v>46199</v>
@@ -26079,7 +26115,7 @@
       </c>
       <c r="D1326">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1326" s="2">
         <v>46199</v>
@@ -26115,7 +26151,7 @@
       </c>
       <c r="D1328">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1328" s="2">
         <v>46199</v>
@@ -26169,7 +26205,7 @@
       </c>
       <c r="D1331">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1331" s="2">
         <v>46199</v>
@@ -26187,7 +26223,7 @@
       </c>
       <c r="D1332">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1332" s="2">
         <v>46199</v>
@@ -26205,7 +26241,7 @@
       </c>
       <c r="D1333">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1333" s="2">
         <v>46199</v>
@@ -26223,7 +26259,7 @@
       </c>
       <c r="D1334">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1334" s="2">
         <v>46199</v>
@@ -26241,7 +26277,7 @@
       </c>
       <c r="D1335">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1335" s="2">
         <v>46199</v>
@@ -26259,7 +26295,7 @@
       </c>
       <c r="D1336">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1336" s="2">
         <v>46199</v>
@@ -26277,7 +26313,7 @@
       </c>
       <c r="D1337">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1337" s="2">
         <v>46199</v>
@@ -26295,7 +26331,7 @@
       </c>
       <c r="D1338">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1338" s="2">
         <v>46199</v>
@@ -26313,7 +26349,7 @@
       </c>
       <c r="D1339">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1339" s="2">
         <v>46199</v>
@@ -26331,7 +26367,7 @@
       </c>
       <c r="D1340">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1340" s="2">
         <v>46199</v>
@@ -26349,7 +26385,7 @@
       </c>
       <c r="D1341">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1341" s="2">
         <v>46199</v>
@@ -26403,7 +26439,7 @@
       </c>
       <c r="D1344">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1344" s="2">
         <v>46199</v>
@@ -26421,7 +26457,7 @@
       </c>
       <c r="D1345">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1345" s="2">
         <v>46199</v>
@@ -26439,7 +26475,7 @@
       </c>
       <c r="D1346">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1346" s="2">
         <v>46199</v>
@@ -26511,7 +26547,7 @@
       </c>
       <c r="D1350">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1350" s="2">
         <v>46199</v>
@@ -26529,7 +26565,7 @@
       </c>
       <c r="D1351">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1351" s="2">
         <v>46199</v>
@@ -26547,7 +26583,7 @@
       </c>
       <c r="D1352">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1352" s="2">
         <v>46199</v>
@@ -26601,7 +26637,7 @@
       </c>
       <c r="D1355">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1355" s="2">
         <v>46199</v>
@@ -26619,7 +26655,7 @@
       </c>
       <c r="D1356">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1356" s="2">
         <v>46199</v>
@@ -26637,7 +26673,7 @@
       </c>
       <c r="D1357">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1357" s="2">
         <v>46199</v>
@@ -26655,7 +26691,7 @@
       </c>
       <c r="D1358">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1358" s="2">
         <v>46199</v>
@@ -26709,7 +26745,7 @@
       </c>
       <c r="D1361">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1361" s="2">
         <v>46199</v>
@@ -26727,7 +26763,7 @@
       </c>
       <c r="D1362">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1362" s="2">
         <v>46199</v>
@@ -26745,7 +26781,7 @@
       </c>
       <c r="D1363">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1363" s="2">
         <v>46199</v>
@@ -26763,7 +26799,7 @@
       </c>
       <c r="D1364">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1364" s="2">
         <v>46199</v>
@@ -26781,7 +26817,7 @@
       </c>
       <c r="D1365">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1365" s="2">
         <v>46199</v>
@@ -26799,7 +26835,7 @@
       </c>
       <c r="D1366">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1366" s="2">
         <v>46199</v>
@@ -26817,7 +26853,7 @@
       </c>
       <c r="D1367">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1367" s="2">
         <v>46199</v>
@@ -26835,7 +26871,7 @@
       </c>
       <c r="D1368">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1368" s="2">
         <v>46199</v>
@@ -26853,7 +26889,7 @@
       </c>
       <c r="D1369">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1369" s="2">
         <v>46199</v>
@@ -26871,7 +26907,7 @@
       </c>
       <c r="D1370">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1370" s="2">
         <v>46199</v>
@@ -26889,7 +26925,7 @@
       </c>
       <c r="D1371">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1371" s="2">
         <v>46199</v>
@@ -26925,7 +26961,7 @@
       </c>
       <c r="D1373">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1373" s="2">
         <v>46199</v>
@@ -26943,7 +26979,7 @@
       </c>
       <c r="D1374">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1374" s="2">
         <v>46199</v>
@@ -26961,7 +26997,7 @@
       </c>
       <c r="D1375">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1375" s="2">
         <v>46199</v>
@@ -26979,7 +27015,7 @@
       </c>
       <c r="D1376">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1376" s="2">
         <v>46199</v>
@@ -27033,7 +27069,7 @@
       </c>
       <c r="D1379">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1379" s="2">
         <v>46199</v>
@@ -27051,7 +27087,7 @@
       </c>
       <c r="D1380">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1380" s="2">
         <v>46199</v>
@@ -27069,7 +27105,7 @@
       </c>
       <c r="D1381">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1381" s="2">
         <v>46199</v>
@@ -27087,7 +27123,7 @@
       </c>
       <c r="D1382">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1382" s="2">
         <v>46199</v>
@@ -27105,7 +27141,7 @@
       </c>
       <c r="D1383">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1383" s="2">
         <v>46199</v>
@@ -27123,7 +27159,7 @@
       </c>
       <c r="D1384">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1384" s="2">
         <v>46199</v>
@@ -27141,7 +27177,7 @@
       </c>
       <c r="D1385">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1385" s="2">
         <v>46199</v>
@@ -27159,7 +27195,7 @@
       </c>
       <c r="D1386">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1386" s="2">
         <v>46199</v>
@@ -27177,7 +27213,7 @@
       </c>
       <c r="D1387">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1387" s="2">
         <v>46199</v>
@@ -27195,7 +27231,7 @@
       </c>
       <c r="D1388">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1388" s="2">
         <v>46199</v>
@@ -27249,7 +27285,7 @@
       </c>
       <c r="D1391">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1391" s="2">
         <v>46199</v>
@@ -27267,7 +27303,7 @@
       </c>
       <c r="D1392">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1392" s="2">
         <v>46199</v>
@@ -27285,7 +27321,7 @@
       </c>
       <c r="D1393">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1393" s="2">
         <v>46199</v>
@@ -27303,7 +27339,7 @@
       </c>
       <c r="D1394">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1394" s="2">
         <v>46199</v>
@@ -27357,7 +27393,7 @@
       </c>
       <c r="D1397">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1397" s="2">
         <v>46199</v>
@@ -27375,7 +27411,7 @@
       </c>
       <c r="D1398">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1398" s="2">
         <v>46199</v>
@@ -27393,7 +27429,7 @@
       </c>
       <c r="D1399">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1399" s="2">
         <v>46199</v>
@@ -27411,7 +27447,7 @@
       </c>
       <c r="D1400">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1400" s="2">
         <v>46199</v>
@@ -27465,7 +27501,7 @@
       </c>
       <c r="D1403">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1403" s="2">
         <v>46199</v>
@@ -27483,7 +27519,7 @@
       </c>
       <c r="D1404">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1404" s="2">
         <v>46199</v>
@@ -27501,7 +27537,7 @@
       </c>
       <c r="D1405">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1405" s="2">
         <v>46199</v>
@@ -27519,7 +27555,7 @@
       </c>
       <c r="D1406">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1406" s="2">
         <v>46199</v>
@@ -27591,7 +27627,7 @@
       </c>
       <c r="D1410">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1410" s="2">
         <v>46199</v>
@@ -27609,7 +27645,7 @@
       </c>
       <c r="D1411">
         <f t="shared" ref="D1411:D1474" si="22">+IF(VLOOKUP(B1411,$K$2:$L$73,2,0)=C1411,3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1411" s="2">
         <v>46199</v>
@@ -27627,7 +27663,7 @@
       </c>
       <c r="D1412">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1412" s="2">
         <v>46199</v>
@@ -27645,7 +27681,7 @@
       </c>
       <c r="D1413">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1413" s="2">
         <v>46199</v>
@@ -27699,7 +27735,7 @@
       </c>
       <c r="D1416">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1416" s="2">
         <v>46199</v>
@@ -27717,7 +27753,7 @@
       </c>
       <c r="D1417">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1417" s="2">
         <v>46199</v>
@@ -27735,7 +27771,7 @@
       </c>
       <c r="D1418">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1418" s="2">
         <v>46199</v>
@@ -27789,7 +27825,7 @@
       </c>
       <c r="D1421">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1421" s="2">
         <v>46199</v>
@@ -27807,7 +27843,7 @@
       </c>
       <c r="D1422">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1422" s="2">
         <v>46199</v>
@@ -27825,7 +27861,7 @@
       </c>
       <c r="D1423">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1423" s="2">
         <v>46199</v>
@@ -27879,7 +27915,7 @@
       </c>
       <c r="D1426">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1426" s="2">
         <v>46199</v>
@@ -27897,7 +27933,7 @@
       </c>
       <c r="D1427">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1427" s="2">
         <v>46199</v>
@@ -27933,7 +27969,7 @@
       </c>
       <c r="D1429">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1429" s="2">
         <v>46199</v>
@@ -27951,7 +27987,7 @@
       </c>
       <c r="D1430">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1430" s="2">
         <v>46199</v>
@@ -27969,7 +28005,7 @@
       </c>
       <c r="D1431">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1431" s="2">
         <v>46199</v>
@@ -28005,7 +28041,7 @@
       </c>
       <c r="D1433">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1433" s="2">
         <v>46199</v>
@@ -28041,7 +28077,7 @@
       </c>
       <c r="D1435">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1435" s="2">
         <v>46199</v>
@@ -28059,7 +28095,7 @@
       </c>
       <c r="D1436">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1436" s="2">
         <v>46199</v>
@@ -28077,7 +28113,7 @@
       </c>
       <c r="D1437">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1437" s="2">
         <v>46199</v>
@@ -28131,7 +28167,7 @@
       </c>
       <c r="D1440">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1440" s="2">
         <v>46199</v>
@@ -28149,7 +28185,7 @@
       </c>
       <c r="D1441">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1441" s="2">
         <v>46199</v>
@@ -28167,7 +28203,7 @@
       </c>
       <c r="D1442">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1442" s="2">
         <v>46199</v>
@@ -28221,7 +28257,7 @@
       </c>
       <c r="D1445">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1445" s="2">
         <v>46199</v>
@@ -28239,7 +28275,7 @@
       </c>
       <c r="D1446">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1446" s="2">
         <v>46199</v>
@@ -28257,7 +28293,7 @@
       </c>
       <c r="D1447">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1447" s="2">
         <v>46199</v>
@@ -28275,7 +28311,7 @@
       </c>
       <c r="D1448">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1448" s="2">
         <v>46199</v>
@@ -28347,7 +28383,7 @@
       </c>
       <c r="D1452">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1452" s="2">
         <v>46199</v>
@@ -28365,7 +28401,7 @@
       </c>
       <c r="D1453">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1453" s="2">
         <v>46199</v>
@@ -28401,7 +28437,7 @@
       </c>
       <c r="D1455">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1455" s="2">
         <v>46200</v>
@@ -28473,7 +28509,7 @@
       </c>
       <c r="D1459">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1459" s="2">
         <v>46200</v>
@@ -28509,7 +28545,7 @@
       </c>
       <c r="D1461">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1461" s="2">
         <v>46200</v>
@@ -28563,7 +28599,7 @@
       </c>
       <c r="D1464">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1464" s="2">
         <v>46200</v>
@@ -28617,7 +28653,7 @@
       </c>
       <c r="D1467">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1467" s="2">
         <v>46200</v>
@@ -28653,7 +28689,7 @@
       </c>
       <c r="D1469">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1469" s="2">
         <v>46200</v>
@@ -28671,7 +28707,7 @@
       </c>
       <c r="D1470">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1470" s="2">
         <v>46200</v>
@@ -28689,7 +28725,7 @@
       </c>
       <c r="D1471">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1471" s="2">
         <v>46200</v>
@@ -28725,7 +28761,7 @@
       </c>
       <c r="D1473">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1473" s="2">
         <v>46200</v>
@@ -28743,7 +28779,7 @@
       </c>
       <c r="D1474">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1474" s="2">
         <v>46200</v>
@@ -28779,7 +28815,7 @@
       </c>
       <c r="D1476">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1476" s="2">
         <v>46200</v>
@@ -28833,7 +28869,7 @@
       </c>
       <c r="D1479">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1479" s="2">
         <v>46200</v>
@@ -28851,7 +28887,7 @@
       </c>
       <c r="D1480">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1480" s="2">
         <v>46200</v>
@@ -28887,7 +28923,7 @@
       </c>
       <c r="D1482">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1482" s="2">
         <v>46200</v>
@@ -28941,7 +28977,7 @@
       </c>
       <c r="D1485">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1485" s="2">
         <v>46200</v>
@@ -28977,7 +29013,7 @@
       </c>
       <c r="D1487">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1487" s="2">
         <v>46200</v>
@@ -28995,7 +29031,7 @@
       </c>
       <c r="D1488">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1488" s="2">
         <v>46200</v>
@@ -29013,7 +29049,7 @@
       </c>
       <c r="D1489">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1489" s="2">
         <v>46200</v>
@@ -29049,7 +29085,7 @@
       </c>
       <c r="D1491">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1491" s="2">
         <v>46200</v>
@@ -29067,7 +29103,7 @@
       </c>
       <c r="D1492">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1492" s="2">
         <v>46200</v>
@@ -29085,7 +29121,7 @@
       </c>
       <c r="D1493">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1493" s="2">
         <v>46200</v>
@@ -29103,7 +29139,7 @@
       </c>
       <c r="D1494">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1494" s="2">
         <v>46200</v>
@@ -29121,7 +29157,7 @@
       </c>
       <c r="D1495">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1495" s="2">
         <v>46200</v>
@@ -29157,7 +29193,7 @@
       </c>
       <c r="D1497">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1497" s="2">
         <v>46200</v>
@@ -29175,7 +29211,7 @@
       </c>
       <c r="D1498">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1498" s="2">
         <v>46200</v>
@@ -29193,7 +29229,7 @@
       </c>
       <c r="D1499">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1499" s="2">
         <v>46200</v>
@@ -29211,7 +29247,7 @@
       </c>
       <c r="D1500">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1500" s="2">
         <v>46200</v>
@@ -29229,7 +29265,7 @@
       </c>
       <c r="D1501">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1501" s="2">
         <v>46200</v>
@@ -29247,7 +29283,7 @@
       </c>
       <c r="D1502">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1502" s="2">
         <v>46200</v>
@@ -29265,7 +29301,7 @@
       </c>
       <c r="D1503">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1503" s="2">
         <v>46200</v>
@@ -29283,7 +29319,7 @@
       </c>
       <c r="D1504">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1504" s="2">
         <v>46200</v>
@@ -29301,7 +29337,7 @@
       </c>
       <c r="D1505">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1505" s="2">
         <v>46200</v>
@@ -29319,7 +29355,7 @@
       </c>
       <c r="D1506">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1506" s="2">
         <v>46200</v>
@@ -29337,7 +29373,7 @@
       </c>
       <c r="D1507">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1507" s="2">
         <v>46200</v>
@@ -29355,7 +29391,7 @@
       </c>
       <c r="D1508">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1508" s="2">
         <v>46200</v>
@@ -29373,7 +29409,7 @@
       </c>
       <c r="D1509">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1509" s="2">
         <v>46200</v>
@@ -29427,7 +29463,7 @@
       </c>
       <c r="D1512">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1512" s="2">
         <v>46200</v>
@@ -29463,7 +29499,7 @@
       </c>
       <c r="D1514">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1514" s="2">
         <v>46200</v>
@@ -29481,7 +29517,7 @@
       </c>
       <c r="D1515">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1515" s="2">
         <v>46200</v>
@@ -29499,7 +29535,7 @@
       </c>
       <c r="D1516">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1516" s="2">
         <v>46200</v>
@@ -29535,7 +29571,7 @@
       </c>
       <c r="D1518">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1518" s="2">
         <v>46200</v>
@@ -29553,7 +29589,7 @@
       </c>
       <c r="D1519">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1519" s="2">
         <v>46200</v>
@@ -29589,7 +29625,7 @@
       </c>
       <c r="D1521">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1521" s="2">
         <v>46200</v>
@@ -29625,7 +29661,7 @@
       </c>
       <c r="D1523">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1523" s="2">
         <v>46200</v>
@@ -29643,7 +29679,7 @@
       </c>
       <c r="D1524">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1524" s="2">
         <v>46200</v>
@@ -29697,7 +29733,7 @@
       </c>
       <c r="D1527">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1527" s="2">
         <v>46200</v>
@@ -29715,7 +29751,7 @@
       </c>
       <c r="D1528">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1528" s="2">
         <v>46200</v>
@@ -29733,7 +29769,7 @@
       </c>
       <c r="D1529">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1529" s="2">
         <v>46200</v>
@@ -29751,7 +29787,7 @@
       </c>
       <c r="D1530">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1530" s="2">
         <v>46200</v>
@@ -29805,7 +29841,7 @@
       </c>
       <c r="D1533">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1533" s="2">
         <v>46200</v>
@@ -29841,7 +29877,7 @@
       </c>
       <c r="D1535">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1535" s="2">
         <v>46200</v>
@@ -29859,7 +29895,7 @@
       </c>
       <c r="D1536">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1536" s="2">
         <v>46200</v>
@@ -29877,7 +29913,7 @@
       </c>
       <c r="D1537">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1537" s="2">
         <v>46200</v>
@@ -29913,7 +29949,7 @@
       </c>
       <c r="D1539">
         <f t="shared" ref="D1539:D1585" si="24">+IF(VLOOKUP(B1539,$K$2:$L$73,2,0)=C1539,3,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1539" s="2">
         <v>46200</v>
@@ -29967,7 +30003,7 @@
       </c>
       <c r="D1542">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1542" s="2">
         <v>46200</v>
@@ -30003,7 +30039,7 @@
       </c>
       <c r="D1544">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1544" s="2">
         <v>46200</v>
@@ -30021,7 +30057,7 @@
       </c>
       <c r="D1545">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1545" s="2">
         <v>46200</v>
@@ -30075,7 +30111,7 @@
       </c>
       <c r="D1548">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1548" s="2">
         <v>46200</v>
@@ -30093,7 +30129,7 @@
       </c>
       <c r="D1549">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1549" s="2">
         <v>46200</v>
@@ -30129,7 +30165,7 @@
       </c>
       <c r="D1551">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1551" s="2">
         <v>46200</v>
@@ -30183,7 +30219,7 @@
       </c>
       <c r="D1554">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1554" s="2">
         <v>46200</v>
@@ -30237,7 +30273,7 @@
       </c>
       <c r="D1557">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1557" s="2">
         <v>46200</v>
@@ -30273,7 +30309,7 @@
       </c>
       <c r="D1559">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1559" s="2">
         <v>46200</v>
@@ -30291,7 +30327,7 @@
       </c>
       <c r="D1560">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1560" s="2">
         <v>46200</v>
@@ -30345,7 +30381,7 @@
       </c>
       <c r="D1563">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1563" s="2">
         <v>46200</v>
@@ -30363,7 +30399,7 @@
       </c>
       <c r="D1564">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1564" s="2">
         <v>46200</v>
@@ -30417,7 +30453,7 @@
       </c>
       <c r="D1567">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1567" s="2">
         <v>46200</v>
@@ -30435,7 +30471,7 @@
       </c>
       <c r="D1568">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1568" s="2">
         <v>46200</v>
@@ -30453,7 +30489,7 @@
       </c>
       <c r="D1569">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1569" s="2">
         <v>46200</v>
@@ -30471,7 +30507,7 @@
       </c>
       <c r="D1570">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1570" s="2">
         <v>46200</v>
@@ -30489,7 +30525,7 @@
       </c>
       <c r="D1571">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1571" s="2">
         <v>46200</v>
@@ -30507,7 +30543,7 @@
       </c>
       <c r="D1572">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1572" s="2">
         <v>46200</v>
@@ -30561,7 +30597,7 @@
       </c>
       <c r="D1575">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1575" s="2">
         <v>46200</v>
@@ -30597,7 +30633,7 @@
       </c>
       <c r="D1577">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1577" s="2">
         <v>46200</v>
@@ -30615,7 +30651,7 @@
       </c>
       <c r="D1578">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1578" s="2">
         <v>46200</v>
@@ -30633,7 +30669,7 @@
       </c>
       <c r="D1579">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1579" s="2">
         <v>46200</v>
@@ -30669,7 +30705,7 @@
       </c>
       <c r="D1581">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1581" s="2">
         <v>46200</v>
@@ -30687,7 +30723,7 @@
       </c>
       <c r="D1582">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1582" s="2">
         <v>46200</v>
@@ -30723,7 +30759,7 @@
       </c>
       <c r="D1584">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1584" s="2">
         <v>46200</v>
